--- a/7RmartSuperMarket/src/main/resources/testdata.xlsx
+++ b/7RmartSuperMarket/src/main/resources/testdata.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{156E88D8-263C-4DCD-98CA-FE4000003CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{81735F18-5C93-478D-8383-34D9626E1A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9B395CD0-E26B-4558-91FA-AE64FD9C23EF}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
   <si>
     <t>username</t>
   </si>
@@ -36,6 +36,12 @@
   </si>
   <si>
     <t>bismi</t>
+  </si>
+  <si>
+    <t>usertype</t>
+  </si>
+  <si>
+    <t>Staff</t>
   </si>
 </sst>
 </file>
@@ -387,26 +393,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75DE34FD-24FA-43E7-9EDE-3E674C60B366}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -414,7 +426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
